--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:16</t>
+    <t xml:space="preserve">2026-09-29 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:04</t>
+    <t xml:space="preserve">2026-09-29 18:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>139.14</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>92.71</v>
+        <v>92.72</v>
       </c>
     </row>
     <row r="3">
@@ -521,10 +521,10 @@
         <v>28.15</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>80.6</v>
+        <v>80.61</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>52.46</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="5">
@@ -535,10 +535,10 @@
         <v>1.82</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45.08</v>
+        <v>45.07</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>43.25</v>
+        <v>43.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:43</t>
+    <t xml:space="preserve">2026-10-05 04:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -524,7 +524,7 @@
         <v>80.61</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>52.45</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         <v>1.82</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45.07</v>
+        <v>45.08</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>43.26</v>
